--- a/samples/edge-cases/edge-sales-list/template.xlsx
+++ b/samples/edge-cases/edge-sales-list/template.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" s="10">
         <f>E5*F5</f>
-        <v>480.0</v>
+        <v>480</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>346</v>
@@ -662,7 +662,7 @@
       </c>
       <c r="G6" s="10">
         <f>E6*F6</f>
-        <v>25600.0</v>
+        <v>25600</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>18432</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" s="10">
         <f>E7*F7</f>
-        <v>294000.0</v>
+        <v>294000</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>211680</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="G8" s="10">
         <f>E8*F8</f>
-        <v>632000.0</v>
+        <v>632000</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>455040</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="G9" s="10">
         <f>E9*F9</f>
-        <v>9900.0</v>
+        <v>9900</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>7128</v>
@@ -818,7 +818,7 @@
       </c>
       <c r="G10" s="10">
         <f>E10*F10</f>
-        <v>2880.0</v>
+        <v>2880</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>2074</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="G11" s="10">
         <f>E11*F11</f>
-        <v>89600.0</v>
+        <v>89600</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>64512</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="G12" s="10">
         <f>E12*F12</f>
-        <v>784000.0</v>
+        <v>784000</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>564480</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="G13" s="10">
         <f>E13*F13</f>
-        <v>1422000.0</v>
+        <v>1422000</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>1023840</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="G14" s="10">
         <f>E14*F14</f>
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>1426</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G15" s="10">
         <f>E15*F15</f>
-        <v>960.0</v>
+        <v>960</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>691</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G16" s="10">
         <f>E16*F16</f>
-        <v>38400.0</v>
+        <v>38400</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>27648</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="10">
         <f>E17*F17</f>
-        <v>392000.0</v>
+        <v>392000</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>282240</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G18" s="10">
         <f>E18*F18</f>
-        <v>790000.0</v>
+        <v>790000</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>568800</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="10">
         <f>E19*F19</f>
-        <v>11880.0</v>
+        <v>11880</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>8554</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G20" s="10">
         <f>E20*F20</f>
-        <v>3360.0</v>
+        <v>3360</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>2419</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G21" s="10">
         <f>E21*F21</f>
-        <v>102400.0</v>
+        <v>102400</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>73728</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G22" s="10">
         <f>E22*F22</f>
-        <v>882000.0</v>
+        <v>882000</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>635040</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G23" s="10">
         <f>E23*F23</f>
-        <v>158000.0</v>
+        <v>158000</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>113760</v>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="G24" s="10">
         <f>E24*F24</f>
-        <v>3960.0</v>
+        <v>3960</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>2851</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G25" s="10">
         <f>E25*F25</f>
-        <v>1440.0</v>
+        <v>1440</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>1037</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="G26" s="10">
         <f>E26*F26</f>
-        <v>51200.0</v>
+        <v>51200</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>36864</v>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G27" s="10">
         <f>E27*F27</f>
-        <v>490000.0</v>
+        <v>490000</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>352800</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G28" s="10">
         <f>E28*F28</f>
-        <v>948000.0</v>
+        <v>948000</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>682560</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G29" s="10">
         <f>E29*F29</f>
-        <v>13860.0</v>
+        <v>13860</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>9979</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="G30" s="10">
         <f>E30*F30</f>
-        <v>3840.0</v>
+        <v>3840</v>
       </c>
       <c r="H30" s="8" t="n">
         <v>2765</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G31" s="10">
         <f>E31*F31</f>
-        <v>115200.0</v>
+        <v>115200</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>82944</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G32" s="10">
         <f>E32*F32</f>
-        <v>98000.0</v>
+        <v>98000</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>70560</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G33" s="10">
         <f>E33*F33</f>
-        <v>316000.0</v>
+        <v>316000</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>227520</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G34" s="10">
         <f>E34*F34</f>
-        <v>5940.0</v>
+        <v>5940</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>4277</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G35" s="10">
         <f>E35*F35</f>
-        <v>1920.0</v>
+        <v>1920</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>1382</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G36" s="10">
         <f>E36*F36</f>
-        <v>64000.0</v>
+        <v>64000</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>46080</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G37" s="10">
         <f>E37*F37</f>
-        <v>588000.0</v>
+        <v>588000</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>423360</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G38" s="10">
         <f>E38*F38</f>
-        <v>1106000.0</v>
+        <v>1106000</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>796320</v>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G39" s="10">
         <f>E39*F39</f>
-        <v>15840.0</v>
+        <v>15840</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>11405</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="G40" s="10">
         <f>E40*F40</f>
-        <v>4320.0</v>
+        <v>4320</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>3110</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="G41" s="10">
         <f>E41*F41</f>
-        <v>12800.0</v>
+        <v>12800</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>9216</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="G42" s="10">
         <f>E42*F42</f>
-        <v>196000.0</v>
+        <v>196000</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>141120</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G43" s="10">
         <f>E43*F43</f>
-        <v>474000.0</v>
+        <v>474000</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>341280</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G44" s="10">
         <f>E44*F44</f>
-        <v>7920.0</v>
+        <v>7920</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>5702</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G45" s="10">
         <f>E45*F45</f>
-        <v>2400.0</v>
+        <v>2400</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>1728</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G46" s="10">
         <f>E46*F46</f>
-        <v>76800.0</v>
+        <v>76800</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>55296</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G47" s="10">
         <f>E47*F47</f>
-        <v>686000.0</v>
+        <v>686000</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>493920</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G48" s="10">
         <f>E48*F48</f>
-        <v>1264000.0</v>
+        <v>1264000</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>910080</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G49" s="10">
         <f>E49*F49</f>
-        <v>17820.0</v>
+        <v>17820</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>12830</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G50" s="10">
         <f>E50*F50</f>
-        <v>480.0</v>
+        <v>480</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>346</v>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G51" s="10">
         <f>E51*F51</f>
-        <v>25600.0</v>
+        <v>25600</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>18432</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="G52" s="10">
         <f>E52*F52</f>
-        <v>294000.0</v>
+        <v>294000</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>211680</v>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G53" s="10">
         <f>E53*F53</f>
-        <v>632000.0</v>
+        <v>632000</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>455040</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G54" s="10">
         <f>E54*F54</f>
-        <v>9900.0</v>
+        <v>9900</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>7128</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G55" s="10">
         <f>E55*F55</f>
-        <v>2880.0</v>
+        <v>2880</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>2074</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G56" s="10">
         <f>E56*F56</f>
-        <v>89600.0</v>
+        <v>89600</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>64512</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G57" s="10">
         <f>E57*F57</f>
-        <v>784000.0</v>
+        <v>784000</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>564480</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G58" s="10">
         <f>E58*F58</f>
-        <v>1422000.0</v>
+        <v>1422000</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>1023840</v>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G59" s="10">
         <f>E59*F59</f>
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>1426</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G60" s="10">
         <f>E60*F60</f>
-        <v>960.0</v>
+        <v>960</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>691</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G61" s="10">
         <f>E61*F61</f>
-        <v>38400.0</v>
+        <v>38400</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>27648</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G62" s="10">
         <f>E62*F62</f>
-        <v>392000.0</v>
+        <v>392000</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>282240</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G63" s="10">
         <f>E63*F63</f>
-        <v>790000.0</v>
+        <v>790000</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>568800</v>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G64" s="10">
         <f>E64*F64</f>
-        <v>11880.0</v>
+        <v>11880</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>8554</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G65" s="10">
         <f>E65*F65</f>
-        <v>3360.0</v>
+        <v>3360</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>2419</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G66" s="10">
         <f>E66*F66</f>
-        <v>102400.0</v>
+        <v>102400</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>73728</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G67" s="10">
         <f>E67*F67</f>
-        <v>882000.0</v>
+        <v>882000</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>635040</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="G68" s="10">
         <f>E68*F68</f>
-        <v>158000.0</v>
+        <v>158000</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>113760</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="G69" s="10">
         <f>E69*F69</f>
-        <v>3960.0</v>
+        <v>3960</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>2851</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G70" s="10">
         <f>E70*F70</f>
-        <v>1440.0</v>
+        <v>1440</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>1037</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="G71" s="10">
         <f>E71*F71</f>
-        <v>51200.0</v>
+        <v>51200</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>36864</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G72" s="10">
         <f>E72*F72</f>
-        <v>490000.0</v>
+        <v>490000</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>352800</v>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G73" s="10">
         <f>E73*F73</f>
-        <v>948000.0</v>
+        <v>948000</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>682560</v>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G74" s="10">
         <f>E74*F74</f>
-        <v>13860.0</v>
+        <v>13860</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>9979</v>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G75" s="10">
         <f>E75*F75</f>
-        <v>3840.0</v>
+        <v>3840</v>
       </c>
       <c r="H75" s="8" t="n">
         <v>2765</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="G76" s="10">
         <f>E76*F76</f>
-        <v>115200.0</v>
+        <v>115200</v>
       </c>
       <c r="H76" s="8" t="n">
         <v>82944</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G77" s="10">
         <f>E77*F77</f>
-        <v>98000.0</v>
+        <v>98000</v>
       </c>
       <c r="H77" s="8" t="n">
         <v>70560</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="G78" s="10">
         <f>E78*F78</f>
-        <v>316000.0</v>
+        <v>316000</v>
       </c>
       <c r="H78" s="8" t="n">
         <v>227520</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G79" s="10">
         <f>E79*F79</f>
-        <v>5940.0</v>
+        <v>5940</v>
       </c>
       <c r="H79" s="8" t="n">
         <v>4277</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="G80" s="10">
         <f>E80*F80</f>
-        <v>1920.0</v>
+        <v>1920</v>
       </c>
       <c r="H80" s="8" t="n">
         <v>1382</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="G81" s="10">
         <f>E81*F81</f>
-        <v>64000.0</v>
+        <v>64000</v>
       </c>
       <c r="H81" s="8" t="n">
         <v>46080</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="G82" s="10">
         <f>E82*F82</f>
-        <v>588000.0</v>
+        <v>588000</v>
       </c>
       <c r="H82" s="8" t="n">
         <v>423360</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G83" s="10">
         <f>E83*F83</f>
-        <v>1106000.0</v>
+        <v>1106000</v>
       </c>
       <c r="H83" s="8" t="n">
         <v>796320</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G84" s="10">
         <f>E84*F84</f>
-        <v>15840.0</v>
+        <v>15840</v>
       </c>
       <c r="H84" s="8" t="n">
         <v>11405</v>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G85" s="10">
         <f>E85*F85</f>
-        <v>4320.0</v>
+        <v>4320</v>
       </c>
       <c r="H85" s="8" t="n">
         <v>3110</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="G86" s="10">
         <f>E86*F86</f>
-        <v>12800.0</v>
+        <v>12800</v>
       </c>
       <c r="H86" s="8" t="n">
         <v>9216</v>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G87" s="10">
         <f>E87*F87</f>
-        <v>196000.0</v>
+        <v>196000</v>
       </c>
       <c r="H87" s="8" t="n">
         <v>141120</v>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="G88" s="10">
         <f>E88*F88</f>
-        <v>474000.0</v>
+        <v>474000</v>
       </c>
       <c r="H88" s="8" t="n">
         <v>341280</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="G89" s="10">
         <f>E89*F89</f>
-        <v>7920.0</v>
+        <v>7920</v>
       </c>
       <c r="H89" s="8" t="n">
         <v>5702</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G90" s="10">
         <f>E90*F90</f>
-        <v>2400.0</v>
+        <v>2400</v>
       </c>
       <c r="H90" s="8" t="n">
         <v>1728</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="G91" s="10">
         <f>E91*F91</f>
-        <v>76800.0</v>
+        <v>76800</v>
       </c>
       <c r="H91" s="8" t="n">
         <v>55296</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G92" s="10">
         <f>E92*F92</f>
-        <v>686000.0</v>
+        <v>686000</v>
       </c>
       <c r="H92" s="8" t="n">
         <v>493920</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G93" s="10">
         <f>E93*F93</f>
-        <v>1264000.0</v>
+        <v>1264000</v>
       </c>
       <c r="H93" s="8" t="n">
         <v>910080</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G94" s="10">
         <f>E94*F94</f>
-        <v>17820.0</v>
+        <v>17820</v>
       </c>
       <c r="H94" s="8" t="n">
         <v>12830</v>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="G95" s="10">
         <f>E95*F95</f>
-        <v>480.0</v>
+        <v>480</v>
       </c>
       <c r="H95" s="8" t="n">
         <v>346</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G96" s="10">
         <f>E96*F96</f>
-        <v>25600.0</v>
+        <v>25600</v>
       </c>
       <c r="H96" s="8" t="n">
         <v>18432</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G97" s="10">
         <f>E97*F97</f>
-        <v>294000.0</v>
+        <v>294000</v>
       </c>
       <c r="H97" s="8" t="n">
         <v>211680</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="G98" s="10">
         <f>E98*F98</f>
-        <v>632000.0</v>
+        <v>632000</v>
       </c>
       <c r="H98" s="8" t="n">
         <v>455040</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G99" s="10">
         <f>E99*F99</f>
-        <v>9900.0</v>
+        <v>9900</v>
       </c>
       <c r="H99" s="8" t="n">
         <v>7128</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G100" s="10">
         <f>E100*F100</f>
-        <v>2880.0</v>
+        <v>2880</v>
       </c>
       <c r="H100" s="8" t="n">
         <v>2074</v>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G101" s="10">
         <f>E101*F101</f>
-        <v>89600.0</v>
+        <v>89600</v>
       </c>
       <c r="H101" s="8" t="n">
         <v>64512</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="G102" s="10">
         <f>E102*F102</f>
-        <v>784000.0</v>
+        <v>784000</v>
       </c>
       <c r="H102" s="8" t="n">
         <v>564480</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G103" s="10">
         <f>E103*F103</f>
-        <v>1422000.0</v>
+        <v>1422000</v>
       </c>
       <c r="H103" s="8" t="n">
         <v>1023840</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="G104" s="10">
         <f>E104*F104</f>
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="H104" s="8" t="n">
         <v>1426</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G105" s="10">
         <f>E105*F105</f>
-        <v>960.0</v>
+        <v>960</v>
       </c>
       <c r="H105" s="8" t="n">
         <v>691</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G106" s="10">
         <f>E106*F106</f>
-        <v>38400.0</v>
+        <v>38400</v>
       </c>
       <c r="H106" s="8" t="n">
         <v>27648</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G107" s="10">
         <f>E107*F107</f>
-        <v>392000.0</v>
+        <v>392000</v>
       </c>
       <c r="H107" s="8" t="n">
         <v>282240</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="G108" s="10">
         <f>E108*F108</f>
-        <v>790000.0</v>
+        <v>790000</v>
       </c>
       <c r="H108" s="8" t="n">
         <v>568800</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G109" s="10">
         <f>E109*F109</f>
-        <v>11880.0</v>
+        <v>11880</v>
       </c>
       <c r="H109" s="8" t="n">
         <v>8554</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="G110" s="10">
         <f>E110*F110</f>
-        <v>3360.0</v>
+        <v>3360</v>
       </c>
       <c r="H110" s="8" t="n">
         <v>2419</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G111" s="10">
         <f>E111*F111</f>
-        <v>102400.0</v>
+        <v>102400</v>
       </c>
       <c r="H111" s="8" t="n">
         <v>73728</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G112" s="10">
         <f>E112*F112</f>
-        <v>882000.0</v>
+        <v>882000</v>
       </c>
       <c r="H112" s="8" t="n">
         <v>635040</v>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G113" s="10">
         <f>E113*F113</f>
-        <v>158000.0</v>
+        <v>158000</v>
       </c>
       <c r="H113" s="8" t="n">
         <v>113760</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G114" s="10">
         <f>E114*F114</f>
-        <v>3960.0</v>
+        <v>3960</v>
       </c>
       <c r="H114" s="8" t="n">
         <v>2851</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G115" s="10">
         <f>E115*F115</f>
-        <v>1440.0</v>
+        <v>1440</v>
       </c>
       <c r="H115" s="8" t="n">
         <v>1037</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G116" s="10">
         <f>E116*F116</f>
-        <v>51200.0</v>
+        <v>51200</v>
       </c>
       <c r="H116" s="8" t="n">
         <v>36864</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="G117" s="10">
         <f>E117*F117</f>
-        <v>490000.0</v>
+        <v>490000</v>
       </c>
       <c r="H117" s="8" t="n">
         <v>352800</v>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="G118" s="10">
         <f>E118*F118</f>
-        <v>948000.0</v>
+        <v>948000</v>
       </c>
       <c r="H118" s="8" t="n">
         <v>682560</v>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="G119" s="10">
         <f>E119*F119</f>
-        <v>13860.0</v>
+        <v>13860</v>
       </c>
       <c r="H119" s="8" t="n">
         <v>9979</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="G120" s="10">
         <f>E120*F120</f>
-        <v>3840.0</v>
+        <v>3840</v>
       </c>
       <c r="H120" s="8" t="n">
         <v>2765</v>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="G121" s="10">
         <f>E121*F121</f>
-        <v>115200.0</v>
+        <v>115200</v>
       </c>
       <c r="H121" s="8" t="n">
         <v>82944</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G122" s="10">
         <f>E122*F122</f>
-        <v>98000.0</v>
+        <v>98000</v>
       </c>
       <c r="H122" s="8" t="n">
         <v>70560</v>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="G123" s="10">
         <f>E123*F123</f>
-        <v>316000.0</v>
+        <v>316000</v>
       </c>
       <c r="H123" s="8" t="n">
         <v>227520</v>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G124" s="10">
         <f>E124*F124</f>
-        <v>5940.0</v>
+        <v>5940</v>
       </c>
       <c r="H124" s="8" t="n">
         <v>4277</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="G125" s="10">
         <f>E125*F125</f>
-        <v>1920.0</v>
+        <v>1920</v>
       </c>
       <c r="H125" s="8" t="n">
         <v>1382</v>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G126" s="10">
         <f>E126*F126</f>
-        <v>64000.0</v>
+        <v>64000</v>
       </c>
       <c r="H126" s="8" t="n">
         <v>46080</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G127" s="10">
         <f>E127*F127</f>
-        <v>588000.0</v>
+        <v>588000</v>
       </c>
       <c r="H127" s="8" t="n">
         <v>423360</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G128" s="10">
         <f>E128*F128</f>
-        <v>1106000.0</v>
+        <v>1106000</v>
       </c>
       <c r="H128" s="8" t="n">
         <v>796320</v>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="G129" s="10">
         <f>E129*F129</f>
-        <v>15840.0</v>
+        <v>15840</v>
       </c>
       <c r="H129" s="8" t="n">
         <v>11405</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="G130" s="10">
         <f>E130*F130</f>
-        <v>4320.0</v>
+        <v>4320</v>
       </c>
       <c r="H130" s="8" t="n">
         <v>3110</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G131" s="10">
         <f>E131*F131</f>
-        <v>12800.0</v>
+        <v>12800</v>
       </c>
       <c r="H131" s="8" t="n">
         <v>9216</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G132" s="10">
         <f>E132*F132</f>
-        <v>196000.0</v>
+        <v>196000</v>
       </c>
       <c r="H132" s="8" t="n">
         <v>141120</v>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G133" s="10">
         <f>E133*F133</f>
-        <v>474000.0</v>
+        <v>474000</v>
       </c>
       <c r="H133" s="8" t="n">
         <v>341280</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="G134" s="10">
         <f>E134*F134</f>
-        <v>7920.0</v>
+        <v>7920</v>
       </c>
       <c r="H134" s="8" t="n">
         <v>5702</v>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="G135" s="10">
         <f>E135*F135</f>
-        <v>2400.0</v>
+        <v>2400</v>
       </c>
       <c r="H135" s="8" t="n">
         <v>1728</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="G136" s="10">
         <f>E136*F136</f>
-        <v>76800.0</v>
+        <v>76800</v>
       </c>
       <c r="H136" s="8" t="n">
         <v>55296</v>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="G137" s="10">
         <f>E137*F137</f>
-        <v>686000.0</v>
+        <v>686000</v>
       </c>
       <c r="H137" s="8" t="n">
         <v>493920</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="G138" s="10">
         <f>E138*F138</f>
-        <v>1264000.0</v>
+        <v>1264000</v>
       </c>
       <c r="H138" s="8" t="n">
         <v>910080</v>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="G139" s="10">
         <f>E139*F139</f>
-        <v>17820.0</v>
+        <v>17820</v>
       </c>
       <c r="H139" s="8" t="n">
         <v>12830</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="G140" s="10">
         <f>E140*F140</f>
-        <v>480.0</v>
+        <v>480</v>
       </c>
       <c r="H140" s="8" t="n">
         <v>346</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G141" s="10">
         <f>E141*F141</f>
-        <v>25600.0</v>
+        <v>25600</v>
       </c>
       <c r="H141" s="8" t="n">
         <v>18432</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="G142" s="10">
         <f>E142*F142</f>
-        <v>294000.0</v>
+        <v>294000</v>
       </c>
       <c r="H142" s="8" t="n">
         <v>211680</v>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="G143" s="10">
         <f>E143*F143</f>
-        <v>632000.0</v>
+        <v>632000</v>
       </c>
       <c r="H143" s="8" t="n">
         <v>455040</v>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="G144" s="10">
         <f>E144*F144</f>
-        <v>9900.0</v>
+        <v>9900</v>
       </c>
       <c r="H144" s="8" t="n">
         <v>7128</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="G145" s="10">
         <f>E145*F145</f>
-        <v>2880.0</v>
+        <v>2880</v>
       </c>
       <c r="H145" s="8" t="n">
         <v>2074</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="G146" s="10">
         <f>E146*F146</f>
-        <v>89600.0</v>
+        <v>89600</v>
       </c>
       <c r="H146" s="8" t="n">
         <v>64512</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="G147" s="10">
         <f>E147*F147</f>
-        <v>784000.0</v>
+        <v>784000</v>
       </c>
       <c r="H147" s="8" t="n">
         <v>564480</v>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="G148" s="10">
         <f>E148*F148</f>
-        <v>1422000.0</v>
+        <v>1422000</v>
       </c>
       <c r="H148" s="8" t="n">
         <v>1023840</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G149" s="10">
         <f>E149*F149</f>
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="H149" s="8" t="n">
         <v>1426</v>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="G150" s="10">
         <f>E150*F150</f>
-        <v>960.0</v>
+        <v>960</v>
       </c>
       <c r="H150" s="8" t="n">
         <v>691</v>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="G151" s="10">
         <f>E151*F151</f>
-        <v>38400.0</v>
+        <v>38400</v>
       </c>
       <c r="H151" s="8" t="n">
         <v>27648</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="G152" s="10">
         <f>E152*F152</f>
-        <v>392000.0</v>
+        <v>392000</v>
       </c>
       <c r="H152" s="8" t="n">
         <v>282240</v>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="G153" s="10">
         <f>E153*F153</f>
-        <v>790000.0</v>
+        <v>790000</v>
       </c>
       <c r="H153" s="8" t="n">
         <v>568800</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G154" s="10">
         <f>E154*F154</f>
-        <v>11880.0</v>
+        <v>11880</v>
       </c>
       <c r="H154" s="8" t="n">
         <v>8554</v>
@@ -6493,11 +6493,11 @@
       <c r="F155" s="14" t="n"/>
       <c r="G155" s="15">
         <f>SUBTOTAL(9,G5:G154)</f>
-        <v>41115780.0</v>
+        <v>41115780</v>
       </c>
       <c r="H155" s="16">
         <f>SUM(H5:H154)</f>
-        <v>29603363.0</v>
+        <v>29603363</v>
       </c>
       <c r="I155" s="14" t="n"/>
       <c r="J155" s="14" t="n"/>
